--- a/artfynd/A 22875-2026 artfynd.xlsx
+++ b/artfynd/A 22875-2026 artfynd.xlsx
@@ -821,11 +821,14 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långemossen, Långemossen, Vg</t>
@@ -882,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födohack på granlåga</t>
+          <t>Födohack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 22875-2026 artfynd.xlsx
+++ b/artfynd/A 22875-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134592561</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591136</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591672</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,6 +1162,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134592516</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134589953</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1375,6 +1405,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134589978</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1496,6 +1531,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590018</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1617,6 +1657,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590062</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1733,6 +1778,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590211</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1845,6 +1895,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590227</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1957,6 +2012,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591212</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2069,6 +2129,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591481</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2181,6 +2246,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134592299</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2297,6 +2367,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591204</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2409,6 +2484,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134592293</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2521,6 +2601,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590083</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2628,6 +2713,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591540</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2740,6 +2830,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590221</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2847,6 +2942,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591612</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2954,6 +3054,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590043</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3061,8 +3166,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591126</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22875-2026 artfynd.xlsx
+++ b/artfynd/A 22875-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2254,57 +2254,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134591204</v>
+        <v>136307448</v>
       </c>
       <c r="B15" t="n">
-        <v>58136</v>
+        <v>57788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spåndals Bergsjö, Tiveden, Vg</t>
+          <t>Långemossen, Långemossen, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474879</v>
+        <v>474855</v>
       </c>
       <c r="R15" t="n">
-        <v>6505596</v>
+        <v>6505530</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2328,22 +2324,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,56 +2365,60 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134591204</t>
+          <t>https://artportalen.se/Sighting/136307448</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134592293</v>
+        <v>134591204</v>
       </c>
       <c r="B16" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Spåndals Bergsjö, Spåndals Bergsjö, Vg</t>
+          <t>Spåndals Bergsjö, Tiveden, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474815</v>
+        <v>474879</v>
       </c>
       <c r="R16" t="n">
-        <v>6505666</v>
+        <v>6505596</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2486,44 +2486,44 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134592293</t>
+          <t>https://artportalen.se/Sighting/134591204</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134590083</v>
+        <v>136307363</v>
       </c>
       <c r="B17" t="n">
-        <v>8460</v>
+        <v>58148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474885</v>
+        <v>474855</v>
       </c>
       <c r="R17" t="n">
-        <v>6505510</v>
+        <v>6505530</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2562,22 +2562,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,16 +2603,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134590083</t>
+          <t>https://artportalen.se/Sighting/136307363</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134591540</v>
+        <v>136307358</v>
       </c>
       <c r="B18" t="n">
-        <v>8449</v>
+        <v>58143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,34 +2620,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>103023</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tutterskulle, Tutterskulle, Vg</t>
+          <t>Långemossen, Långemossen, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475022</v>
+        <v>474855</v>
       </c>
       <c r="R18" t="n">
-        <v>6505575</v>
+        <v>6505530</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2679,7 +2684,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2689,7 +2694,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,33 +2720,33 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134591540</t>
+          <t>https://artportalen.se/Sighting/136307358</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134590221</v>
+        <v>134592293</v>
       </c>
       <c r="B19" t="n">
-        <v>56706</v>
+        <v>5201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>206046</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2752,19 +2757,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långemossen, Långemossen, Vg</t>
+          <t>Spåndals Bergsjö, Spåndals Bergsjö, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474880</v>
+        <v>474815</v>
       </c>
       <c r="R19" t="n">
-        <v>6505532</v>
+        <v>6505666</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2796,7 +2801,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2806,7 +2811,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2832,16 +2837,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134590221</t>
+          <t>https://artportalen.se/Sighting/134592293</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134591612</v>
+        <v>134590083</v>
       </c>
       <c r="B20" t="n">
-        <v>98060</v>
+        <v>8460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,34 +2854,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tutterskulle, Tutterskulle, Vg</t>
+          <t>Långemossen, Långemossen, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475033</v>
+        <v>474885</v>
       </c>
       <c r="R20" t="n">
-        <v>6505568</v>
+        <v>6505510</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2908,7 +2918,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2918,7 +2928,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2944,16 +2954,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134591612</t>
+          <t>https://artportalen.se/Sighting/134590083</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134590043</v>
+        <v>134591540</v>
       </c>
       <c r="B21" t="n">
-        <v>98063</v>
+        <v>8449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2961,34 +2971,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långemossen, Långemossen, Vg</t>
+          <t>Tutterskulle, Tutterskulle, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474885</v>
+        <v>475022</v>
       </c>
       <c r="R21" t="n">
-        <v>6505501</v>
+        <v>6505575</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3020,7 +3030,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3030,7 +3040,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,51 +3066,56 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134590043</t>
+          <t>https://artportalen.se/Sighting/134591540</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134591126</v>
+        <v>134590221</v>
       </c>
       <c r="B22" t="n">
-        <v>98063</v>
+        <v>56706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221946</v>
+        <v>206046</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långemossen, Långemossen, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474956</v>
+        <v>474880</v>
       </c>
       <c r="R22" t="n">
-        <v>6505583</v>
+        <v>6505532</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3132,7 +3147,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3142,7 +3157,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3167,6 +3182,342 @@
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590221</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134591612</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tutterskulle, Tutterskulle, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>475033</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6505568</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591612</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134590043</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långemossen, Långemossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>474885</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6505501</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590043</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134591126</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långemossen, Långemossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>474956</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6505583</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134591126</t>
         </is>
@@ -3195,6 +3546,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
